--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 5 Sep 2026, 06.04 | Dicetak: 5 Sep 2026, 06.50</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 6 Sep 2026, 06.04 | Dicetak: 6 Sep 2026, 07.43</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>28,53</t>
+    <t>29,29</t>
   </si>
   <si>
     <t>1801</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>14,01</t>
+    <t>14,04</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>10,3</t>
+    <t>10,09</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>13,83</t>
+    <t>17,03</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>15,22</t>
+    <t>16,1</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>78,92</t>
+    <t>78,89</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>15,77</t>
+    <t>19,28</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>29,21</t>
+    <t>26,87</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>32,91</t>
+    <t>32,18</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>52,71</t>
+    <t>53,64</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>35,46</t>
+    <t>33,57</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>87,44</t>
+    <t>85,92</t>
   </si>
   <si>
     <t>1813</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>5,91</t>
+    <t>8,45</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>17,19</t>
+    <t>25,38</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>14092</v>
+        <v>14465</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>944</v>
+        <v>1162</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>1310</v>
+        <v>1386</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>458</v>
+        <v>560</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>1139</v>
+        <v>1048</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>906</v>
+        <v>886</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>846</v>
+        <v>861</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>639</v>
+        <v>605</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2173</v>
+        <v>2135</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>203</v>
+        <v>290</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>14092</v>
+        <v>14465</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 6 Sep 2026, 06.04 | Dicetak: 6 Sep 2026, 07.43</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 7 Sep 2026, 12.04 | Dicetak: 7 Sep 2026, 15.56</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>29,29</t>
+    <t>31,34</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>99,9</t>
+    <t>99,6</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>14,04</t>
+    <t>15,67</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>10,09</t>
+    <t>13,7</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>17,03</t>
+    <t>17,63</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>16,1</t>
+    <t>16,82</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>78,89</t>
+    <t>80,38</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>19,28</t>
+    <t>23,03</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>26,87</t>
+    <t>32,62</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>32,18</t>
+    <t>31,75</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>53,64</t>
+    <t>62,24</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>33,57</t>
+    <t>31,63</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>85,92</t>
+    <t>84,91</t>
   </si>
   <si>
     <t>1813</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>8,45</t>
+    <t>11,16</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>25,38</t>
+    <t>37,78</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>14465</v>
+        <v>15478</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>387</v>
+        <v>432</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>587</v>
+        <v>797</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>1162</v>
+        <v>1203</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>1386</v>
+        <v>1448</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>3173</v>
+        <v>3233</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>560</v>
+        <v>669</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>1048</v>
+        <v>1272</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>861</v>
+        <v>999</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>605</v>
+        <v>570</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2135</v>
+        <v>2110</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>290</v>
+        <v>383</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>217</v>
+        <v>323</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>14465</v>
+        <v>15478</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 7 Sep 2026, 12.04 | Dicetak: 7 Sep 2026, 15.56</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 8 Sep 2026, 06.04 | Dicetak: 8 Sep 2026, 07.17</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>31,34</t>
+    <t>32,07</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>99,6</t>
+    <t>99,8</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>15,67</t>
+    <t>21,12</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>13,7</t>
+    <t>13,76</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>17,63</t>
+    <t>18,65</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>16,82</t>
+    <t>17,15</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>80,38</t>
+    <t>80,03</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>23,03</t>
+    <t>22,93</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>32,62</t>
+    <t>32,23</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>31,75</t>
+    <t>31,13</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>62,24</t>
+    <t>63,55</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>31,63</t>
+    <t>33,85</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>84,91</t>
+    <t>83,62</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>25,77</t>
+    <t>25,61</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>11,16</t>
+    <t>11,57</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>37,78</t>
+    <t>50,88</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>15478</v>
+        <v>15836</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>432</v>
+        <v>582</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>1203</v>
+        <v>1273</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>3233</v>
+        <v>3219</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>1272</v>
+        <v>1257</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>874</v>
+        <v>857</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>999</v>
+        <v>1020</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>570</v>
+        <v>610</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2110</v>
+        <v>2078</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>323</v>
+        <v>435</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>15478</v>
+        <v>15836</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 8 Sep 2026, 06.04 | Dicetak: 8 Sep 2026, 07.17</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 9 Sep 2026, 06.04 | Dicetak: 9 Sep 2026, 08.15</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>32,07</t>
+    <t>34,62</t>
   </si>
   <si>
     <t>1801</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>21,12</t>
+    <t>21,7</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>13,76</t>
+    <t>14,65</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>18,65</t>
+    <t>18,82</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>17,15</t>
+    <t>27,91</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>80,03</t>
+    <t>78,92</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>22,93</t>
+    <t>27,71</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>32,23</t>
+    <t>32,26</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>31,13</t>
+    <t>30,26</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>63,55</t>
+    <t>66,23</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>33,85</t>
+    <t>38,01</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>83,62</t>
+    <t>82,82</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>25,61</t>
+    <t>25,45</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>11,57</t>
+    <t>14,28</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>50,88</t>
+    <t>50,18</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>15836</v>
+        <v>17096</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>800</v>
+        <v>852</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>1273</v>
+        <v>1284</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>1476</v>
+        <v>2402</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>3219</v>
+        <v>3174</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>666</v>
+        <v>805</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>857</v>
+        <v>833</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>1020</v>
+        <v>1063</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>610</v>
+        <v>685</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2078</v>
+        <v>2058</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>397</v>
+        <v>490</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>15836</v>
+        <v>17096</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 9 Sep 2026, 06.04 | Dicetak: 9 Sep 2026, 08.15</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 10 Sep 2026, 06.04 | Dicetak: 10 Sep 2026, 08.07</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>34,62</t>
+    <t>39,11</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>99,8</t>
+    <t>99,6</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>21,7</t>
+    <t>23,69</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>14,65</t>
+    <t>15,97</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>18,82</t>
+    <t>18,49</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>27,91</t>
+    <t>49,56</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>78,92</t>
+    <t>78,64</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>27,71</t>
+    <t>27,92</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>32,26</t>
+    <t>32,13</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>30,26</t>
+    <t>28,99</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>66,23</t>
+    <t>78,94</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>38,01</t>
+    <t>42,45</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>82,82</t>
+    <t>82,29</t>
   </si>
   <si>
     <t>1813</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>14,28</t>
+    <t>15,33</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>50,18</t>
+    <t>48,54</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>17096</v>
+        <v>19316</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>598</v>
+        <v>653</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>852</v>
+        <v>929</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>1284</v>
+        <v>1262</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>2402</v>
+        <v>4266</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>3174</v>
+        <v>3163</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>833</v>
+        <v>798</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>1063</v>
+        <v>1267</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>685</v>
+        <v>765</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2058</v>
+        <v>2045</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>490</v>
+        <v>526</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>17096</v>
+        <v>19316</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 10 Sep 2026, 06.04 | Dicetak: 10 Sep 2026, 08.07</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 11 Sep 2026, 06.04 | Dicetak: 11 Sep 2026, 07.29</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>39,11</t>
+    <t>45,26</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>99,6</t>
+    <t>99,9</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>23,69</t>
+    <t>24,82</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>15,97</t>
+    <t>29,26</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>18,49</t>
+    <t>18,48</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>49,56</t>
+    <t>73,08</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>78,64</t>
+    <t>79,04</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>27,92</t>
+    <t>28,19</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>32,13</t>
+    <t>32,18</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>28,99</t>
+    <t>28,3</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>78,94</t>
+    <t>83,12</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>42,45</t>
+    <t>45,89</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>82,29</t>
+    <t>81,69</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>25,45</t>
+    <t>25,29</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>15,33</t>
+    <t>17,95</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>48,54</t>
+    <t>48,19</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>19316</v>
+        <v>22353</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>653</v>
+        <v>684</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>929</v>
+        <v>1702</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>4266</v>
+        <v>6290</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>3163</v>
+        <v>3179</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>798</v>
+        <v>779</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>1267</v>
+        <v>1334</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>765</v>
+        <v>827</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2045</v>
+        <v>2030</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>526</v>
+        <v>616</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>19316</v>
+        <v>22353</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 11 Sep 2026, 06.04 | Dicetak: 11 Sep 2026, 07.29</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 13 Sep 2026, 12.04 | Dicetak: 13 Sep 2026, 14.36</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>45,26</t>
+    <t>50,46</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>99,9</t>
+    <t>81,8</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>24,82</t>
+    <t>27,14</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>29,26</t>
+    <t>39,68</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>18,48</t>
+    <t>18,65</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>73,08</t>
+    <t>82,98</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>79,04</t>
+    <t>79,94</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>28,19</t>
+    <t>35,8</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>32,18</t>
+    <t>35,41</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>28,3</t>
+    <t>25,61</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>83,12</t>
+    <t>85,67</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>45,89</t>
+    <t>48,72</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>81,69</t>
+    <t>84,95</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>25,29</t>
+    <t>24,96</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>17,95</t>
+    <t>37,3</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>48,19</t>
+    <t>56,61</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>22353</v>
+        <v>24920</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>1010</v>
+        <v>827</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>684</v>
+        <v>748</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>1702</v>
+        <v>2308</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>1261</v>
+        <v>1273</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>6290</v>
+        <v>7142</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>3179</v>
+        <v>3215</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>819</v>
+        <v>1040</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>1255</v>
+        <v>1381</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>779</v>
+        <v>705</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>1334</v>
+        <v>1375</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>827</v>
+        <v>878</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2030</v>
+        <v>2111</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>616</v>
+        <v>1280</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>412</v>
+        <v>484</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>22353</v>
+        <v>24920</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 13 Sep 2026, 12.04 | Dicetak: 13 Sep 2026, 14.36</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 15 Sep 2026, 06.04 | Dicetak: 15 Sep 2026, 06.36</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>50,46</t>
+    <t>61,3</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>81,8</t>
+    <t>79,53</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>27,14</t>
+    <t>32,44</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>39,68</t>
+    <t>47,33</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>18,65</t>
+    <t>23,84</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>82,98</t>
+    <t>96,33</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>79,94</t>
+    <t>79,54</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>35,8</t>
+    <t>95,9</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>35,41</t>
+    <t>35,15</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>25,61</t>
+    <t>40,61</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>85,67</t>
+    <t>91,65</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>48,72</t>
+    <t>49,28</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>84,95</t>
+    <t>96,78</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>24,96</t>
+    <t>24,47</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>37,3</t>
+    <t>52,59</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>56,61</t>
+    <t>83,04</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>24920</v>
+        <v>30272</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>827</v>
+        <v>804</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>748</v>
+        <v>894</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>2308</v>
+        <v>2753</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>1273</v>
+        <v>1627</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>7142</v>
+        <v>8291</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>3215</v>
+        <v>3199</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>1040</v>
+        <v>2786</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>1381</v>
+        <v>1371</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>705</v>
+        <v>1118</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>1375</v>
+        <v>1471</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>878</v>
+        <v>888</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2111</v>
+        <v>2405</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>1280</v>
+        <v>1805</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>484</v>
+        <v>710</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>24920</v>
+        <v>30272</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
   <si>
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 15 Sep 2026, 06.04 | Dicetak: 15 Sep 2026, 06.36</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 16 Sep 2026, 06.04 | Dicetak: 16 Sep 2026, 08.56</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>61,3</t>
+    <t>94,43</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>79,53</t>
+    <t>92,38</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>32,44</t>
+    <t>85,78</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>47,33</t>
+    <t>85,14</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>23,84</t>
+    <t>88,07</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>96,33</t>
+    <t>100,03</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>79,54</t>
+    <t>100,02</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,25 +118,19 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>95,9</t>
-  </si>
-  <si>
     <t>1808</t>
   </si>
   <si>
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>35,15</t>
-  </si>
-  <si>
     <t>1809</t>
   </si>
   <si>
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>40,61</t>
+    <t>95,53</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +139,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>91,65</t>
+    <t>100</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +148,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>49,28</t>
+    <t>100,06</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,25 +157,19 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>96,78</t>
-  </si>
-  <si>
     <t>1813</t>
   </si>
   <si>
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>24,47</t>
-  </si>
-  <si>
     <t>1871</t>
   </si>
   <si>
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>52,59</t>
+    <t>85,81</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +178,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>83,04</t>
+    <t>99,77</t>
   </si>
   <si>
     <t/>
@@ -759,7 +747,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>30272</v>
+        <v>46634</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +764,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>804</v>
+        <v>934</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +781,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>894</v>
+        <v>2364</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +798,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>2753</v>
+        <v>4952</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +815,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>1627</v>
+        <v>6010</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +832,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>8291</v>
+        <v>8610</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +849,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>3199</v>
+        <v>4023</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,160 +866,160 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>2786</v>
+        <v>2906</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="C14" s="9">
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>1371</v>
+        <v>3901</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C15" s="9">
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>1118</v>
+        <v>2630</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" s="9">
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>1471</v>
+        <v>1605</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C17" s="9">
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>888</v>
+        <v>1803</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" s="9">
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2405</v>
+        <v>2485</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C19" s="9">
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>150</v>
+        <v>613</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C20" s="9">
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>1805</v>
+        <v>2945</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C21" s="9">
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>710</v>
+        <v>853</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C22" s="12">
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>30272</v>
+        <v>46634</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>
